--- a/data/07_QUARTERLY_WEIGHTING/2024/T4/312X_1D/LFS_SAMPLE_DATA_2024_T4_312X_1D_SUMMARY_OF_Xs_EST_DES_WEIGHT.xlsx
+++ b/data/07_QUARTERLY_WEIGHTING/2024/T4/312X_1D/LFS_SAMPLE_DATA_2024_T4_312X_1D_SUMMARY_OF_Xs_EST_DES_WEIGHT.xlsx
@@ -1933,943 +1933,943 @@
         </is>
       </c>
       <c r="B2">
-        <v>4408482.898452759</v>
+        <v>2435086.577816167</v>
       </c>
       <c r="C2">
-        <v>946009.4449157715</v>
+        <v>617097.8219488491</v>
       </c>
       <c r="D2">
-        <v>897245.6761169434</v>
+        <v>553058.3261356597</v>
       </c>
       <c r="E2">
-        <v>882639.2987060547</v>
+        <v>417616.0721064299</v>
       </c>
       <c r="F2">
-        <v>638032.8248291016</v>
+        <v>348636.2633479309</v>
       </c>
       <c r="G2">
-        <v>825098.6602020264</v>
+        <v>369271.1880225898</v>
       </c>
       <c r="H2">
-        <v>644199.4504241943</v>
+        <v>372976.6165509298</v>
       </c>
       <c r="I2">
-        <v>415112.5469360352</v>
+        <v>245730.2234402738</v>
       </c>
       <c r="J2">
-        <v>343486.3421783447</v>
+        <v>181342.2359124488</v>
       </c>
       <c r="K2">
-        <v>353102.7899017334</v>
+        <v>142837.4718534084</v>
       </c>
       <c r="L2">
-        <v>143393.4237518311</v>
+        <v>92009.33744812843</v>
       </c>
       <c r="M2">
-        <v>213671.2919616699</v>
+        <v>123319.6329647891</v>
       </c>
       <c r="N2">
-        <v>3829421.964439392</v>
+        <v>2028247.831144195</v>
       </c>
       <c r="O2">
-        <v>550929.4535179138</v>
+        <v>289113.8729801912</v>
       </c>
       <c r="P2">
-        <v>520574.638671875</v>
+        <v>304186.9462738459</v>
       </c>
       <c r="Q2">
-        <v>438195.7258605957</v>
+        <v>249148.3050379899</v>
       </c>
       <c r="R2">
-        <v>484588.8992881775</v>
+        <v>234501.2002687122</v>
       </c>
       <c r="S2">
-        <v>631632.0369148254</v>
+        <v>271550.5505709473</v>
       </c>
       <c r="T2">
-        <v>430043.5943450928</v>
+        <v>232246.34146675</v>
       </c>
       <c r="U2">
-        <v>310293.7313995361</v>
+        <v>186151.7943184116</v>
       </c>
       <c r="V2">
-        <v>274298.5526351929</v>
+        <v>138351.6975941383</v>
       </c>
       <c r="W2">
-        <v>139285.0891418457</v>
+        <v>88947.0143559572</v>
       </c>
       <c r="X2">
-        <v>149554.7839508057</v>
+        <v>93444.74756504585</v>
       </c>
       <c r="Y2">
-        <v>221991.7363967896</v>
+        <v>107974.1196508589</v>
       </c>
       <c r="Z2">
-        <v>4525323.142944336</v>
+        <v>2379789.993137228</v>
       </c>
       <c r="AA2">
-        <v>1158424.232330322</v>
+        <v>713605.3510025752</v>
       </c>
       <c r="AB2">
-        <v>1374761.134384155</v>
+        <v>714320.2934210722</v>
       </c>
       <c r="AC2">
-        <v>1046085.441375732</v>
+        <v>474842.2164412421</v>
       </c>
       <c r="AD2">
-        <v>714990.7503967285</v>
+        <v>429500.8705300601</v>
       </c>
       <c r="AE2">
-        <v>796465.666595459</v>
+        <v>436193.2225619344</v>
       </c>
       <c r="AF2">
-        <v>576441.471786499</v>
+        <v>326884.009823251</v>
       </c>
       <c r="AG2">
-        <v>428589.2324676514</v>
+        <v>247075.4326166104</v>
       </c>
       <c r="AH2">
-        <v>246707.7724914551</v>
+        <v>157783.0028769656</v>
       </c>
       <c r="AI2">
-        <v>173584.4572906494</v>
+        <v>117515.0096540628</v>
       </c>
       <c r="AJ2">
-        <v>159965.2857208252</v>
+        <v>97289.58699739751</v>
       </c>
       <c r="AK2">
-        <v>197670.8505096436</v>
+        <v>139928.2721946591</v>
       </c>
       <c r="AL2">
-        <v>3636818.659683228</v>
+        <v>1875736.170475752</v>
       </c>
       <c r="AM2">
-        <v>540392.1434288025</v>
+        <v>308758.9446495421</v>
       </c>
       <c r="AN2">
-        <v>714797.4414482117</v>
+        <v>307050.7836088759</v>
       </c>
       <c r="AO2">
-        <v>743725.445224762</v>
+        <v>327857.6582335688</v>
       </c>
       <c r="AP2">
-        <v>488095.1835327148</v>
+        <v>271088.4323724417</v>
       </c>
       <c r="AQ2">
-        <v>505834.4157371521</v>
+        <v>274138.5892162345</v>
       </c>
       <c r="AR2">
-        <v>364910.7671890259</v>
+        <v>214559.1721369746</v>
       </c>
       <c r="AS2">
-        <v>208797.0710945129</v>
+        <v>122207.2284201306</v>
       </c>
       <c r="AT2">
-        <v>184342.0081596375</v>
+        <v>105073.0950995565</v>
       </c>
       <c r="AU2">
-        <v>148263.9691085815</v>
+        <v>81646.23152250759</v>
       </c>
       <c r="AV2">
-        <v>121985.6654853821</v>
+        <v>77512.87986907827</v>
       </c>
       <c r="AW2">
-        <v>167027.0813369751</v>
+        <v>127537.6000545318</v>
       </c>
       <c r="AX2">
-        <v>1581840.998779297</v>
+        <v>778058.7630522089</v>
       </c>
       <c r="AY2">
-        <v>2436057.771362305</v>
+        <v>1283512.995983936</v>
       </c>
       <c r="AZ2">
-        <v>1664980.715576172</v>
+        <v>704228.3694779117</v>
       </c>
       <c r="BA2">
-        <v>2813051.857666016</v>
+        <v>1431173.78313253</v>
       </c>
       <c r="BB2">
-        <v>295997.2412109375</v>
+        <v>158882.6842105263</v>
       </c>
       <c r="BC2">
-        <v>320505.1892700195</v>
+        <v>177797.2894736842</v>
       </c>
       <c r="BD2">
-        <v>312282.3854370117</v>
+        <v>181580.2105263158</v>
       </c>
       <c r="BE2">
-        <v>399415.5413818359</v>
+        <v>226975.2631578948</v>
       </c>
       <c r="BF2">
-        <v>228093.965637207</v>
+        <v>121227.512345679</v>
       </c>
       <c r="BG2">
-        <v>332534.7155151367</v>
+        <v>204640.9382716049</v>
       </c>
       <c r="BH2">
-        <v>242440.617980957</v>
+        <v>130124.9444444445</v>
       </c>
       <c r="BI2">
-        <v>362002.8106689453</v>
+        <v>217987.0864197531</v>
       </c>
       <c r="BJ2">
-        <v>201847.5740966797</v>
+        <v>114195.5260115607</v>
       </c>
       <c r="BK2">
-        <v>327613.0789794922</v>
+        <v>187115.5606936416</v>
       </c>
       <c r="BL2">
-        <v>203403.3797607422</v>
+        <v>125202.323699422</v>
       </c>
       <c r="BM2">
-        <v>345524.7136230469</v>
+        <v>198122.3583815029</v>
       </c>
       <c r="BN2">
-        <v>94586.75628662109</v>
+        <v>55627.86451612904</v>
       </c>
       <c r="BO2">
-        <v>164262.9018554688</v>
+        <v>87684.60000000001</v>
       </c>
       <c r="BP2">
-        <v>109123.5947875977</v>
+        <v>59399.24516129033</v>
       </c>
       <c r="BQ2">
-        <v>156096.1049804688</v>
+        <v>89570.29032258065</v>
       </c>
       <c r="BR2">
-        <v>219448.4621582031</v>
+        <v>124408.8523489933</v>
       </c>
       <c r="BS2">
-        <v>259662.9888916016</v>
+        <v>158666.3624161074</v>
       </c>
       <c r="BT2">
-        <v>213691.5545654297</v>
+        <v>128014.9060402685</v>
       </c>
       <c r="BU2">
-        <v>220702.1472167969</v>
+        <v>138833.067114094</v>
       </c>
       <c r="BV2">
-        <v>49093.15475463867</v>
+        <v>29366.45161290323</v>
       </c>
       <c r="BW2">
-        <v>96719.38192749023</v>
+        <v>53927.48387096775</v>
       </c>
       <c r="BX2">
-        <v>58861.26745605469</v>
+        <v>38443.35483870968</v>
       </c>
       <c r="BY2">
-        <v>102527.988861084</v>
+        <v>60334.70967741936</v>
       </c>
       <c r="BZ2">
-        <v>107674.2811279297</v>
+        <v>40336.53846153846</v>
       </c>
       <c r="CA2">
-        <v>151110.7452392578</v>
+        <v>57815.70512820513</v>
       </c>
       <c r="CB2">
-        <v>61336.05981445313</v>
+        <v>25546.47435897436</v>
       </c>
       <c r="CC2">
-        <v>136255.5474853516</v>
+        <v>55126.60256410256</v>
       </c>
       <c r="CD2">
-        <v>101726.9870605469</v>
+        <v>81556.17647058825</v>
       </c>
       <c r="CE2">
-        <v>148407.9523925781</v>
+        <v>107447.0261437909</v>
       </c>
       <c r="CF2">
-        <v>100065.9138183594</v>
+        <v>72494.37908496734</v>
       </c>
       <c r="CG2">
-        <v>144306.4067382813</v>
+        <v>106152.4836601307</v>
       </c>
       <c r="CH2">
-        <v>21246.86006164551</v>
+        <v>18117.75308641975</v>
       </c>
       <c r="CI2">
-        <v>29998.11796569824</v>
+        <v>28216.17283950617</v>
       </c>
       <c r="CJ2">
-        <v>17589.18589782715</v>
+        <v>16335.67901234568</v>
       </c>
       <c r="CK2">
-        <v>29911.56385803223</v>
+        <v>28513.18518518519</v>
       </c>
       <c r="CL2">
-        <v>22352.50253295898</v>
+        <v>15307.87037037037</v>
       </c>
       <c r="CM2">
-        <v>33220.03421020508</v>
+        <v>23712.19135802469</v>
       </c>
       <c r="CN2">
-        <v>18321.86178588867</v>
+        <v>14107.25308641975</v>
       </c>
       <c r="CO2">
-        <v>45958.15856933594</v>
+        <v>30915.89506172839</v>
       </c>
       <c r="CP2">
-        <v>134891.9188232422</v>
+        <v>88652.49999999999</v>
       </c>
       <c r="CQ2">
-        <v>175467.6184082031</v>
+        <v>116707.0886075949</v>
       </c>
       <c r="CR2">
-        <v>120197.3004150391</v>
+        <v>80797.21518987342</v>
       </c>
       <c r="CS2">
-        <v>174336.8454589844</v>
+        <v>116707.0886075949</v>
       </c>
       <c r="CT2">
-        <v>58008.57006835938</v>
+        <v>41690.43113772455</v>
       </c>
       <c r="CU2">
-        <v>116307.9368896484</v>
+        <v>68837.68862275449</v>
       </c>
       <c r="CV2">
-        <v>62449.05023193359</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="CW2">
-        <v>120698.154296875</v>
+        <v>84350.40718562873</v>
       </c>
       <c r="CX2">
-        <v>36063.50668334961</v>
+        <v>38163.70481927711</v>
       </c>
       <c r="CY2">
-        <v>33166.32968139648</v>
+        <v>32711.74698795181</v>
       </c>
       <c r="CZ2">
-        <v>32323.12847900391</v>
+        <v>33207.37951807229</v>
       </c>
       <c r="DA2">
-        <v>53022.58285522461</v>
+        <v>52041.41566265061</v>
       </c>
       <c r="DB2">
-        <v>90933.50512695313</v>
+        <v>61276.03125</v>
       </c>
       <c r="DC2">
-        <v>144942.7376708984</v>
+        <v>85036.125</v>
       </c>
       <c r="DD2">
-        <v>122634.1400146484</v>
+        <v>67528.6875</v>
       </c>
       <c r="DE2">
-        <v>171157.9149169922</v>
+        <v>103794.09375</v>
       </c>
       <c r="DF2">
-        <v>74867.18896484375</v>
+        <v>49000.61728395062</v>
       </c>
       <c r="DG2">
-        <v>85627.9296875</v>
+        <v>61740.77777777777</v>
       </c>
       <c r="DH2">
-        <v>59965.24536132813</v>
+        <v>44100.55555555555</v>
       </c>
       <c r="DI2">
-        <v>105507.3120117188</v>
+        <v>77420.97530864197</v>
       </c>
       <c r="DJ2">
-        <v>128089.1275634766</v>
+        <v>124908.1646341463</v>
       </c>
       <c r="DK2">
-        <v>140858.2978515625</v>
+        <v>126033.4634146342</v>
       </c>
       <c r="DL2">
-        <v>122418.8438110352</v>
+        <v>115905.7743902439</v>
       </c>
       <c r="DM2">
-        <v>205949.7382202148</v>
+        <v>182298.4024390244</v>
       </c>
       <c r="DN2">
-        <v>69113.85424804688</v>
+        <v>61122.57851239669</v>
       </c>
       <c r="DO2">
-        <v>84399.74499511719</v>
+        <v>76114.90909090909</v>
       </c>
       <c r="DP2">
-        <v>50024.99523925781</v>
+        <v>47283.50413223141</v>
       </c>
       <c r="DQ2">
-        <v>70479.81567382813</v>
+        <v>86494.21487603306</v>
       </c>
       <c r="DR2">
-        <v>15172.44750976563</v>
+        <v>12476.0245398773</v>
       </c>
       <c r="DS2">
-        <v>26161.4680480957</v>
+        <v>23250.77300613497</v>
       </c>
       <c r="DT2">
-        <v>22659.67776489258</v>
+        <v>19281.12883435583</v>
       </c>
       <c r="DU2">
-        <v>27391.37377929688</v>
+        <v>22967.22699386503</v>
       </c>
       <c r="DV2">
-        <v>112284.6325683594</v>
+        <v>38316</v>
       </c>
       <c r="DW2">
-        <v>102428.840637207</v>
+        <v>45319.99999999999</v>
       </c>
       <c r="DX2">
-        <v>114339.9086303711</v>
+        <v>48615.99999999999</v>
       </c>
       <c r="DY2">
-        <v>114130.4612121582</v>
+        <v>52323.99999999999</v>
       </c>
       <c r="DZ2">
-        <v>59665.80322265625</v>
+        <v>31828.71812080537</v>
       </c>
       <c r="EA2">
-        <v>63303.37939453125</v>
+        <v>35605.0067114094</v>
       </c>
       <c r="EB2">
-        <v>48304.85083007813</v>
+        <v>25894.55033557047</v>
       </c>
       <c r="EC2">
-        <v>64070.95690917969</v>
+        <v>33986.59731543624</v>
       </c>
       <c r="ED2">
-        <v>31848.67886352539</v>
+        <v>16413.18238993711</v>
       </c>
       <c r="EE2">
-        <v>41336.69708251953</v>
+        <v>20003.56603773585</v>
       </c>
       <c r="EF2">
-        <v>19011.35064697266</v>
+        <v>8719.503144654089</v>
       </c>
       <c r="EG2">
-        <v>36801.04095458984</v>
+        <v>17951.91823899371</v>
       </c>
       <c r="EH2">
-        <v>39710.40502929688</v>
+        <v>15794.25641025641</v>
       </c>
       <c r="EI2">
-        <v>48839.03210449219</v>
+        <v>17074.87179487179</v>
       </c>
       <c r="EJ2">
-        <v>55850.03668212891</v>
+        <v>17928.61538461538</v>
       </c>
       <c r="EK2">
-        <v>54137.89709472656</v>
+        <v>20916.71794871795</v>
       </c>
       <c r="EL2">
-        <v>11874.712890625</v>
+        <v>9256.000000000002</v>
       </c>
       <c r="EM2">
-        <v>9566.355285644531</v>
+        <v>6942.000000000002</v>
       </c>
       <c r="EN2">
-        <v>11150.88557434082</v>
+        <v>8677.500000000002</v>
       </c>
       <c r="EO2">
-        <v>10953.34230041504</v>
+        <v>8214.700000000003</v>
       </c>
       <c r="EP2">
-        <v>10209.06927490234</v>
+        <v>10570.31055900621</v>
       </c>
       <c r="EQ2">
-        <v>21034.98809814453</v>
+        <v>17441.01242236025</v>
       </c>
       <c r="ER2">
-        <v>15005.63946533203</v>
+        <v>9513.27950310559</v>
       </c>
       <c r="ES2">
-        <v>17402.23815917969</v>
+        <v>13741.40372670808</v>
       </c>
       <c r="ET2">
-        <v>67938.18908691406</v>
+        <v>19865</v>
       </c>
       <c r="EU2">
-        <v>166360.8497314453</v>
+        <v>45210</v>
       </c>
       <c r="EV2">
-        <v>126478.8435058594</v>
+        <v>31510</v>
       </c>
       <c r="EW2">
-        <v>161114.9732666016</v>
+        <v>41100</v>
       </c>
       <c r="EX2">
-        <v>76777.06079101563</v>
+        <v>70243.71428571428</v>
       </c>
       <c r="EY2">
-        <v>84137.07385253906</v>
+        <v>81441.98757763975</v>
       </c>
       <c r="EZ2">
-        <v>76385.33642578125</v>
+        <v>74315.81366459627</v>
       </c>
       <c r="FA2">
-        <v>88435.31127929688</v>
+        <v>85514.08695652173</v>
       </c>
       <c r="FB2">
-        <v>129526.9857177734</v>
+        <v>23680.71951219512</v>
       </c>
       <c r="FC2">
-        <v>307868.1326904297</v>
+        <v>35162.28048780488</v>
       </c>
       <c r="FD2">
-        <v>129234.0931396484</v>
+        <v>25833.51219512195</v>
       </c>
       <c r="FE2">
-        <v>235046.227722168</v>
+        <v>38032.67073170732</v>
       </c>
       <c r="FF2">
-        <v>28867.12405395508</v>
+        <v>32630.73825503356</v>
       </c>
       <c r="FG2">
-        <v>47470.78814697266</v>
+        <v>48583.54362416107</v>
       </c>
       <c r="FH2">
-        <v>37565.29010009766</v>
+        <v>39156.88590604027</v>
       </c>
       <c r="FI2">
-        <v>32670.84112548828</v>
+        <v>34080.9932885906</v>
       </c>
       <c r="FJ2">
-        <v>55116.46856689453</v>
+        <v>18126.97435897436</v>
       </c>
       <c r="FK2">
-        <v>79533.64239501953</v>
+        <v>24805.33333333333</v>
       </c>
       <c r="FL2">
-        <v>54486.30261230469</v>
+        <v>14787.79487179487</v>
       </c>
       <c r="FM2">
-        <v>88772.45471191406</v>
+        <v>31006.66666666666</v>
       </c>
       <c r="FN2">
-        <v>96077.06103515625</v>
+        <v>58632.72727272727</v>
       </c>
       <c r="FO2">
-        <v>70196.1376953125</v>
+        <v>42508.72727272727</v>
       </c>
       <c r="FP2">
-        <v>79786.03881835938</v>
+        <v>48372</v>
       </c>
       <c r="FQ2">
-        <v>100456.6040039063</v>
+        <v>61564.36363636363</v>
       </c>
       <c r="FR2">
-        <v>114290.2341308594</v>
+        <v>46323.9477124183</v>
       </c>
       <c r="FS2">
-        <v>120538.8604125977</v>
+        <v>60397.04575163397</v>
       </c>
       <c r="FT2">
-        <v>118652.6946411133</v>
+        <v>49255.84313725489</v>
       </c>
       <c r="FU2">
-        <v>126705.0096435547</v>
+        <v>64501.69934640522</v>
       </c>
       <c r="FV2">
-        <v>43247.57052612305</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="FW2">
-        <v>32352.03155517578</v>
+        <v>22430.91603053435</v>
       </c>
       <c r="FX2">
-        <v>44302.95367431641</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="FY2">
-        <v>58692.35870361328</v>
+        <v>42222.90076335878</v>
       </c>
       <c r="FZ2">
-        <v>82398.3046875</v>
+        <v>34075.56626506025</v>
       </c>
       <c r="GA2">
-        <v>54932.203125</v>
+        <v>22717.04417670683</v>
       </c>
       <c r="GB2">
-        <v>13733.05078125</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="GC2">
-        <v>27466.1015625</v>
+        <v>11358.52208835341</v>
       </c>
       <c r="GD2">
-        <v>306739.9072265625</v>
+        <v>88898.64473684212</v>
       </c>
       <c r="GE2">
-        <v>402944.1727294922</v>
+        <v>105921.7894736842</v>
       </c>
       <c r="GF2">
-        <v>304736.5280761719</v>
+        <v>96464.48684210528</v>
       </c>
       <c r="GG2">
-        <v>379808.6964111328</v>
+        <v>105921.7894736842</v>
       </c>
       <c r="GH2">
-        <v>35117.3369140625</v>
+        <v>17794.86419753087</v>
       </c>
       <c r="GI2">
-        <v>143727.8048095703</v>
+        <v>33365.37037037037</v>
       </c>
       <c r="GJ2">
-        <v>108410.1628417969</v>
+        <v>20019.22222222223</v>
       </c>
       <c r="GK2">
-        <v>125149.7523193359</v>
+        <v>35589.72839506173</v>
       </c>
       <c r="GL2">
-        <v>128639.3366699219</v>
+        <v>60537.387283237</v>
       </c>
       <c r="GM2">
-        <v>98585.91430664063</v>
+        <v>45403.04046242775</v>
       </c>
       <c r="GN2">
-        <v>81184.62744140625</v>
+        <v>38523.79190751445</v>
       </c>
       <c r="GO2">
-        <v>108118.5883789063</v>
+        <v>52282.28901734105</v>
       </c>
       <c r="GP2">
-        <v>22042.56652832031</v>
+        <v>12256.9870967742</v>
       </c>
       <c r="GQ2">
-        <v>66600.01599121094</v>
+        <v>36770.96129032259</v>
       </c>
       <c r="GR2">
-        <v>36881.72241210938</v>
+        <v>20742.5935483871</v>
       </c>
       <c r="GS2">
-        <v>63256.28015136719</v>
+        <v>31113.89032258065</v>
       </c>
       <c r="GT2">
-        <v>211202.8186035156</v>
+        <v>86545.28859060403</v>
       </c>
       <c r="GU2">
-        <v>190427.6174316406</v>
+        <v>99166.47651006712</v>
       </c>
       <c r="GV2">
-        <v>184950.8747558594</v>
+        <v>82939.23489932886</v>
       </c>
       <c r="GW2">
-        <v>175986.5393066406</v>
+        <v>93757.39597315436</v>
       </c>
       <c r="GX2">
-        <v>22636.69287109375</v>
+        <v>11212.64516129032</v>
       </c>
       <c r="GY2">
-        <v>32009.94738769531</v>
+        <v>13882.32258064516</v>
       </c>
       <c r="GZ2">
-        <v>22369.70739746094</v>
+        <v>8542.967741935485</v>
       </c>
       <c r="HA2">
-        <v>38810.11340332031</v>
+        <v>16018.06451612903</v>
       </c>
       <c r="HB2">
-        <v>142708.1545410156</v>
+        <v>145211.5384615384</v>
       </c>
       <c r="HC2">
-        <v>132085.5460205078</v>
+        <v>135799.6794871795</v>
       </c>
       <c r="HD2">
-        <v>130675.7342529297</v>
+        <v>141177.8846153846</v>
       </c>
       <c r="HE2">
-        <v>156158.6331176758</v>
+        <v>165379.8076923077</v>
       </c>
       <c r="HF2">
-        <v>131981.6223144531</v>
+        <v>95796.14379084969</v>
       </c>
       <c r="HG2">
-        <v>166978.0813598633</v>
+        <v>133337.8758169935</v>
       </c>
       <c r="HH2">
-        <v>120750.7232055664</v>
+        <v>88028.88888888891</v>
       </c>
       <c r="HI2">
-        <v>117927.9946899414</v>
+        <v>95796.14379084969</v>
       </c>
       <c r="HJ2">
-        <v>22191.32257080078</v>
+        <v>24355.01234567901</v>
       </c>
       <c r="HK2">
-        <v>22578.0553894043</v>
+        <v>21978.91358024691</v>
       </c>
       <c r="HL2">
-        <v>15325.076171875</v>
+        <v>15147.62962962963</v>
       </c>
       <c r="HM2">
-        <v>19217.60214233398</v>
+        <v>20196.83950617284</v>
       </c>
       <c r="HN2">
-        <v>30671.77998352051</v>
+        <v>27914.35185185185</v>
       </c>
       <c r="HO2">
-        <v>23080.9861907959</v>
+        <v>22211.41975308642</v>
       </c>
       <c r="HP2">
-        <v>18304.55323791504</v>
+        <v>18309.41358024691</v>
       </c>
       <c r="HQ2">
-        <v>19995.4859161377</v>
+        <v>21310.95679012345</v>
       </c>
       <c r="HR2">
-        <v>168671.1983642578</v>
+        <v>69575.37974683543</v>
       </c>
       <c r="HS2">
-        <v>173840.2359924316</v>
+        <v>87530.31645569619</v>
       </c>
       <c r="HT2">
-        <v>86188.21475219727</v>
+        <v>58353.54430379746</v>
       </c>
       <c r="HU2">
-        <v>141424.3297119141</v>
+        <v>80797.2151898734</v>
       </c>
       <c r="HV2">
-        <v>63746.59545898438</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="HW2">
-        <v>106694.7081298828</v>
+        <v>70776.77844311377</v>
       </c>
       <c r="HX2">
-        <v>76327.84631347656</v>
+        <v>55264.05988023952</v>
       </c>
       <c r="HY2">
-        <v>80466.30688476563</v>
+        <v>54294.51497005988</v>
       </c>
       <c r="HZ2">
-        <v>90447.21884155273</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="IA2">
-        <v>91060.13900756836</v>
+        <v>48571.98795180723</v>
       </c>
       <c r="IB2">
-        <v>89144.06875610352</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="IC2">
-        <v>84477.33901977539</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="ID2">
-        <v>131404.5615234375</v>
+        <v>140059.5</v>
       </c>
       <c r="IE2">
-        <v>116878.9415283203</v>
+        <v>118800.46875</v>
       </c>
       <c r="IF2">
-        <v>131347.6142578125</v>
+        <v>127554.1875</v>
       </c>
       <c r="IG2">
-        <v>130958.4440917969</v>
+        <v>127554.1875</v>
       </c>
       <c r="IH2">
-        <v>119691.5768737793</v>
+        <v>79381</v>
       </c>
       <c r="II2">
-        <v>151295.2855529785</v>
+        <v>95061.1975308642</v>
       </c>
       <c r="IJ2">
-        <v>113468.7731018066</v>
+        <v>73500.92592592593</v>
       </c>
       <c r="IK2">
-        <v>139529.7712402344</v>
+        <v>93101.17283950617</v>
       </c>
       <c r="IL2">
-        <v>97653.71081542969</v>
+        <v>50638.44512195123</v>
       </c>
       <c r="IM2">
-        <v>123024.009765625</v>
+        <v>64142.03048780488</v>
       </c>
       <c r="IN2">
-        <v>122756.9658813477</v>
+        <v>51763.74390243903</v>
       </c>
       <c r="IO2">
-        <v>122748.6596069336</v>
+        <v>60766.13414634147</v>
       </c>
       <c r="IP2">
-        <v>300222.1003417969</v>
+        <v>53049.78512396694</v>
       </c>
       <c r="IQ2">
-        <v>299234.7979736328</v>
+        <v>61122.57851239669</v>
       </c>
       <c r="IR2">
-        <v>366688.8677978516</v>
+        <v>54203.04132231405</v>
       </c>
       <c r="IS2">
-        <v>326490.6356201172</v>
+        <v>62275.8347107438</v>
       </c>
       <c r="IT2">
-        <v>68064.72453308105</v>
+        <v>31190.06134969325</v>
       </c>
       <c r="IU2">
-        <v>70217.0173034668</v>
+        <v>30339.42331288343</v>
       </c>
       <c r="IV2">
-        <v>81474.15878295898</v>
+        <v>32607.79141104294</v>
       </c>
       <c r="IW2">
-        <v>71210.35330200195</v>
+        <v>31473.60736196319</v>
       </c>
       <c r="IX2">
-        <v>118636.4149169922</v>
+        <v>46555.99999999999</v>
       </c>
       <c r="IY2">
-        <v>122831.495300293</v>
+        <v>41199.99999999999</v>
       </c>
       <c r="IZ2">
-        <v>134877.5102539063</v>
+        <v>49027.99999999999</v>
       </c>
       <c r="JA2">
-        <v>145082.3936157227</v>
+        <v>53147.99999999999</v>
       </c>
       <c r="JB2">
-        <v>34437.85606384277</v>
+        <v>26973.48993288591</v>
       </c>
       <c r="JC2">
-        <v>50478.46473693848</v>
+        <v>39920.76510067114</v>
       </c>
       <c r="JD2">
-        <v>39596.41110229492</v>
+        <v>32907.6577181208</v>
       </c>
       <c r="JE2">
-        <v>46185.14227294922</v>
+        <v>44775.9932885906</v>
       </c>
       <c r="JF2">
-        <v>227215.1658325195</v>
+        <v>67191.46540880503</v>
       </c>
       <c r="JG2">
-        <v>190630.9176635742</v>
+        <v>56933.22641509434</v>
       </c>
       <c r="JH2">
-        <v>250002.6293334961</v>
+        <v>73346.40880503145</v>
       </c>
       <c r="JI2">
-        <v>238642.5345458984</v>
+        <v>63088.16981132075</v>
       </c>
       <c r="JJ2">
-        <v>128025.756149292</v>
+        <v>73848.82051282052</v>
       </c>
       <c r="JK2">
-        <v>95606.76109313965</v>
+        <v>50370.87179487179</v>
       </c>
       <c r="JL2">
-        <v>145834.3167419434</v>
+        <v>72141.33333333333</v>
       </c>
       <c r="JM2">
-        <v>130194.6992645264</v>
+        <v>62323.28205128205</v>
       </c>
       <c r="JN2">
-        <v>43695.21019744873</v>
+        <v>38643.8</v>
       </c>
       <c r="JO2">
-        <v>32904.56284713745</v>
+        <v>29156.4</v>
       </c>
       <c r="JP2">
-        <v>36876.07884216309</v>
+        <v>32280.3</v>
       </c>
       <c r="JQ2">
-        <v>40970.2685585022</v>
+        <v>36792.6</v>
       </c>
       <c r="JR2">
-        <v>54372.17523193359</v>
+        <v>46509.36645962734</v>
       </c>
       <c r="JS2">
-        <v>58429.41122436523</v>
+        <v>49680.4596273292</v>
       </c>
       <c r="JT2">
-        <v>56226.12835693359</v>
+        <v>49151.94409937889</v>
       </c>
       <c r="JU2">
-        <v>54984.77224731445</v>
+        <v>45452.33540372671</v>
       </c>
       <c r="JV2">
-        <v>91675.04922485352</v>
+        <v>28769.99999999999</v>
       </c>
       <c r="JW2">
-        <v>161171.2774963379</v>
+        <v>50004.99999999999</v>
       </c>
       <c r="JX2">
-        <v>80648.53570556641</v>
+        <v>29454.99999999999</v>
       </c>
       <c r="JY2">
-        <v>141800.4077148438</v>
+        <v>47949.99999999999</v>
       </c>
       <c r="JZ2">
-        <v>299525.4259643555</v>
+        <v>130307.1801242236</v>
       </c>
       <c r="KA2">
-        <v>326309.0322875977</v>
+        <v>133361.2546583851</v>
       </c>
       <c r="KB2">
-        <v>234392.6777954102</v>
+        <v>94676.3105590062</v>
       </c>
       <c r="KC2">
-        <v>280092.392578125</v>
+        <v>114018.7826086957</v>
       </c>
       <c r="KD2">
-        <v>80550.1708984375</v>
+        <v>60278.19512195121</v>
       </c>
       <c r="KE2">
-        <v>86267.35577392578</v>
+        <v>66018.97560975609</v>
       </c>
       <c r="KF2">
-        <v>67785.53344726563</v>
+        <v>48079.03658536585</v>
       </c>
       <c r="KG2">
-        <v>99899.70349121094</v>
+        <v>76782.93902439025</v>
       </c>
       <c r="KH2">
-        <v>114958.1827087402</v>
+        <v>47858.41610738255</v>
       </c>
       <c r="KI2">
-        <v>142540.8352203369</v>
+        <v>58010.20134228187</v>
       </c>
       <c r="KJ2">
-        <v>114118.469619751</v>
+        <v>57285.07382550335</v>
       </c>
       <c r="KK2">
-        <v>144125.0939025879</v>
+        <v>65261.47651006711</v>
       </c>
       <c r="KL2">
-        <v>53602.15167236328</v>
+        <v>22897.23076923077</v>
       </c>
       <c r="KM2">
-        <v>75849.84545898438</v>
+        <v>31483.6923076923</v>
       </c>
       <c r="KN2">
-        <v>41205.28686523438</v>
+        <v>19081.02564102564</v>
       </c>
       <c r="KO2">
-        <v>80506.30206298828</v>
+        <v>34345.84615384615</v>
       </c>
       <c r="KP2">
-        <v>202910.0549621582</v>
+        <v>206680.3636363636</v>
       </c>
       <c r="KQ2">
-        <v>191835.2662658691</v>
+        <v>237462.5454545454</v>
       </c>
       <c r="KR2">
-        <v>157838.8239440918</v>
+        <v>177364</v>
       </c>
       <c r="KS2">
-        <v>225569.4076538086</v>
+        <v>237462.5454545455</v>
       </c>
       <c r="KT2">
-        <v>179084.1236572266</v>
+        <v>45737.56862745097</v>
       </c>
       <c r="KU2">
-        <v>122191.4125366211</v>
+        <v>45737.56862745097</v>
       </c>
       <c r="KV2">
-        <v>149612.2430114746</v>
+        <v>50428.60130718954</v>
       </c>
       <c r="KW2">
-        <v>198989.490234375</v>
+        <v>51601.35947712418</v>
       </c>
       <c r="KX2">
-        <v>24502.69729614258</v>
+        <v>59375.95419847329</v>
       </c>
       <c r="KY2">
-        <v>28146.12422180176</v>
+        <v>59375.95419847329</v>
       </c>
       <c r="KZ2">
-        <v>23084.74444580078</v>
+        <v>48160.49618320611</v>
       </c>
       <c r="LA2">
-        <v>31926.95672607422</v>
+        <v>71910.87786259543</v>
       </c>
       <c r="LB2">
-        <v>37915284.14466095</v>
+        <v>20450740.2356909</v>
       </c>
     </row>
     <row r="3">
@@ -2879,943 +2879,943 @@
         </is>
       </c>
       <c r="B3">
-        <v>4408482.898452759</v>
+        <v>2435086.577816167</v>
       </c>
       <c r="C3">
-        <v>946009.4449157715</v>
+        <v>617097.8219488491</v>
       </c>
       <c r="D3">
-        <v>897245.6761169434</v>
+        <v>553058.3261356597</v>
       </c>
       <c r="E3">
-        <v>882639.2987060547</v>
+        <v>417616.0721064299</v>
       </c>
       <c r="F3">
-        <v>638032.8248291016</v>
+        <v>348636.2633479309</v>
       </c>
       <c r="G3">
-        <v>825098.6602020264</v>
+        <v>369271.1880225898</v>
       </c>
       <c r="H3">
-        <v>644199.4504241943</v>
+        <v>372976.6165509298</v>
       </c>
       <c r="I3">
-        <v>415112.5469360352</v>
+        <v>245730.2234402738</v>
       </c>
       <c r="J3">
-        <v>343486.3421783447</v>
+        <v>181342.2359124488</v>
       </c>
       <c r="K3">
-        <v>353102.7899017334</v>
+        <v>142837.4718534084</v>
       </c>
       <c r="L3">
-        <v>143393.4237518311</v>
+        <v>92009.33744812843</v>
       </c>
       <c r="M3">
-        <v>213671.2919616699</v>
+        <v>123319.6329647891</v>
       </c>
       <c r="N3">
-        <v>3829421.964439392</v>
+        <v>2028247.831144195</v>
       </c>
       <c r="O3">
-        <v>550929.4535179138</v>
+        <v>289113.8729801912</v>
       </c>
       <c r="P3">
-        <v>520574.638671875</v>
+        <v>304186.9462738459</v>
       </c>
       <c r="Q3">
-        <v>438195.7258605957</v>
+        <v>249148.3050379899</v>
       </c>
       <c r="R3">
-        <v>484588.8992881775</v>
+        <v>234501.2002687122</v>
       </c>
       <c r="S3">
-        <v>631632.0369148254</v>
+        <v>271550.5505709473</v>
       </c>
       <c r="T3">
-        <v>430043.5943450928</v>
+        <v>232246.34146675</v>
       </c>
       <c r="U3">
-        <v>310293.7313995361</v>
+        <v>186151.7943184116</v>
       </c>
       <c r="V3">
-        <v>274298.5526351929</v>
+        <v>138351.6975941383</v>
       </c>
       <c r="W3">
-        <v>139285.0891418457</v>
+        <v>88947.0143559572</v>
       </c>
       <c r="X3">
-        <v>149554.7839508057</v>
+        <v>93444.74756504585</v>
       </c>
       <c r="Y3">
-        <v>221991.7363967896</v>
+        <v>107974.1196508589</v>
       </c>
       <c r="Z3">
-        <v>4525323.142944336</v>
+        <v>2379789.993137228</v>
       </c>
       <c r="AA3">
-        <v>1158424.232330322</v>
+        <v>713605.3510025752</v>
       </c>
       <c r="AB3">
-        <v>1374761.134384155</v>
+        <v>714320.2934210722</v>
       </c>
       <c r="AC3">
-        <v>1046085.441375732</v>
+        <v>474842.2164412421</v>
       </c>
       <c r="AD3">
-        <v>714990.7503967285</v>
+        <v>429500.8705300601</v>
       </c>
       <c r="AE3">
-        <v>796465.666595459</v>
+        <v>436193.2225619344</v>
       </c>
       <c r="AF3">
-        <v>576441.471786499</v>
+        <v>326884.009823251</v>
       </c>
       <c r="AG3">
-        <v>428589.2324676514</v>
+        <v>247075.4326166104</v>
       </c>
       <c r="AH3">
-        <v>246707.7724914551</v>
+        <v>157783.0028769656</v>
       </c>
       <c r="AI3">
-        <v>173584.4572906494</v>
+        <v>117515.0096540628</v>
       </c>
       <c r="AJ3">
-        <v>159965.2857208252</v>
+        <v>97289.58699739751</v>
       </c>
       <c r="AK3">
-        <v>197670.8505096436</v>
+        <v>139928.2721946591</v>
       </c>
       <c r="AL3">
-        <v>3636818.659683228</v>
+        <v>1875736.170475752</v>
       </c>
       <c r="AM3">
-        <v>540392.1434288025</v>
+        <v>308758.9446495421</v>
       </c>
       <c r="AN3">
-        <v>714797.4414482117</v>
+        <v>307050.7836088759</v>
       </c>
       <c r="AO3">
-        <v>743725.445224762</v>
+        <v>327857.6582335688</v>
       </c>
       <c r="AP3">
-        <v>488095.1835327148</v>
+        <v>271088.4323724417</v>
       </c>
       <c r="AQ3">
-        <v>505834.4157371521</v>
+        <v>274138.5892162345</v>
       </c>
       <c r="AR3">
-        <v>364910.7671890259</v>
+        <v>214559.1721369746</v>
       </c>
       <c r="AS3">
-        <v>208797.0710945129</v>
+        <v>122207.2284201306</v>
       </c>
       <c r="AT3">
-        <v>184342.0081596375</v>
+        <v>105073.0950995565</v>
       </c>
       <c r="AU3">
-        <v>148263.9691085815</v>
+        <v>81646.23152250759</v>
       </c>
       <c r="AV3">
-        <v>121985.6654853821</v>
+        <v>77512.87986907827</v>
       </c>
       <c r="AW3">
-        <v>167027.0813369751</v>
+        <v>127537.6000545318</v>
       </c>
       <c r="AX3">
-        <v>1581840.998779297</v>
+        <v>778058.7630522089</v>
       </c>
       <c r="AY3">
-        <v>2436057.771362305</v>
+        <v>1283512.995983936</v>
       </c>
       <c r="AZ3">
-        <v>1664980.715576172</v>
+        <v>704228.3694779117</v>
       </c>
       <c r="BA3">
-        <v>2813051.857666016</v>
+        <v>1431173.78313253</v>
       </c>
       <c r="BB3">
-        <v>295997.2412109375</v>
+        <v>158882.6842105263</v>
       </c>
       <c r="BC3">
-        <v>320505.1892700195</v>
+        <v>177797.2894736842</v>
       </c>
       <c r="BD3">
-        <v>312282.3854370117</v>
+        <v>181580.2105263158</v>
       </c>
       <c r="BE3">
-        <v>399415.5413818359</v>
+        <v>226975.2631578948</v>
       </c>
       <c r="BF3">
-        <v>228093.965637207</v>
+        <v>121227.512345679</v>
       </c>
       <c r="BG3">
-        <v>332534.7155151367</v>
+        <v>204640.9382716049</v>
       </c>
       <c r="BH3">
-        <v>242440.617980957</v>
+        <v>130124.9444444445</v>
       </c>
       <c r="BI3">
-        <v>362002.8106689453</v>
+        <v>217987.0864197531</v>
       </c>
       <c r="BJ3">
-        <v>201847.5740966797</v>
+        <v>114195.5260115607</v>
       </c>
       <c r="BK3">
-        <v>327613.0789794922</v>
+        <v>187115.5606936416</v>
       </c>
       <c r="BL3">
-        <v>203403.3797607422</v>
+        <v>125202.323699422</v>
       </c>
       <c r="BM3">
-        <v>345524.7136230469</v>
+        <v>198122.3583815029</v>
       </c>
       <c r="BN3">
-        <v>94586.75628662109</v>
+        <v>55627.86451612904</v>
       </c>
       <c r="BO3">
-        <v>164262.9018554688</v>
+        <v>87684.60000000001</v>
       </c>
       <c r="BP3">
-        <v>109123.5947875977</v>
+        <v>59399.24516129033</v>
       </c>
       <c r="BQ3">
-        <v>156096.1049804688</v>
+        <v>89570.29032258065</v>
       </c>
       <c r="BR3">
-        <v>219448.4621582031</v>
+        <v>124408.8523489933</v>
       </c>
       <c r="BS3">
-        <v>259662.9888916016</v>
+        <v>158666.3624161074</v>
       </c>
       <c r="BT3">
-        <v>213691.5545654297</v>
+        <v>128014.9060402685</v>
       </c>
       <c r="BU3">
-        <v>220702.1472167969</v>
+        <v>138833.067114094</v>
       </c>
       <c r="BV3">
-        <v>49093.15475463867</v>
+        <v>29366.45161290323</v>
       </c>
       <c r="BW3">
-        <v>96719.38192749023</v>
+        <v>53927.48387096775</v>
       </c>
       <c r="BX3">
-        <v>58861.26745605469</v>
+        <v>38443.35483870968</v>
       </c>
       <c r="BY3">
-        <v>102527.988861084</v>
+        <v>60334.70967741936</v>
       </c>
       <c r="BZ3">
-        <v>107674.2811279297</v>
+        <v>40336.53846153846</v>
       </c>
       <c r="CA3">
-        <v>151110.7452392578</v>
+        <v>57815.70512820513</v>
       </c>
       <c r="CB3">
-        <v>61336.05981445313</v>
+        <v>25546.47435897436</v>
       </c>
       <c r="CC3">
-        <v>136255.5474853516</v>
+        <v>55126.60256410256</v>
       </c>
       <c r="CD3">
-        <v>101726.9870605469</v>
+        <v>81556.17647058825</v>
       </c>
       <c r="CE3">
-        <v>148407.9523925781</v>
+        <v>107447.0261437909</v>
       </c>
       <c r="CF3">
-        <v>100065.9138183594</v>
+        <v>72494.37908496734</v>
       </c>
       <c r="CG3">
-        <v>144306.4067382813</v>
+        <v>106152.4836601307</v>
       </c>
       <c r="CH3">
-        <v>21246.86006164551</v>
+        <v>18117.75308641975</v>
       </c>
       <c r="CI3">
-        <v>29998.11796569824</v>
+        <v>28216.17283950617</v>
       </c>
       <c r="CJ3">
-        <v>17589.18589782715</v>
+        <v>16335.67901234568</v>
       </c>
       <c r="CK3">
-        <v>29911.56385803223</v>
+        <v>28513.18518518519</v>
       </c>
       <c r="CL3">
-        <v>22352.50253295898</v>
+        <v>15307.87037037037</v>
       </c>
       <c r="CM3">
-        <v>33220.03421020508</v>
+        <v>23712.19135802469</v>
       </c>
       <c r="CN3">
-        <v>18321.86178588867</v>
+        <v>14107.25308641975</v>
       </c>
       <c r="CO3">
-        <v>45958.15856933594</v>
+        <v>30915.89506172839</v>
       </c>
       <c r="CP3">
-        <v>134891.9188232422</v>
+        <v>88652.49999999999</v>
       </c>
       <c r="CQ3">
-        <v>175467.6184082031</v>
+        <v>116707.0886075949</v>
       </c>
       <c r="CR3">
-        <v>120197.3004150391</v>
+        <v>80797.21518987342</v>
       </c>
       <c r="CS3">
-        <v>174336.8454589844</v>
+        <v>116707.0886075949</v>
       </c>
       <c r="CT3">
-        <v>58008.57006835938</v>
+        <v>41690.43113772455</v>
       </c>
       <c r="CU3">
-        <v>116307.9368896484</v>
+        <v>68837.68862275449</v>
       </c>
       <c r="CV3">
-        <v>62449.05023193359</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="CW3">
-        <v>120698.154296875</v>
+        <v>84350.40718562873</v>
       </c>
       <c r="CX3">
-        <v>36063.50668334961</v>
+        <v>38163.70481927711</v>
       </c>
       <c r="CY3">
-        <v>33166.32968139648</v>
+        <v>32711.74698795181</v>
       </c>
       <c r="CZ3">
-        <v>32323.12847900391</v>
+        <v>33207.37951807229</v>
       </c>
       <c r="DA3">
-        <v>53022.58285522461</v>
+        <v>52041.41566265061</v>
       </c>
       <c r="DB3">
-        <v>90933.50512695313</v>
+        <v>61276.03125</v>
       </c>
       <c r="DC3">
-        <v>144942.7376708984</v>
+        <v>85036.125</v>
       </c>
       <c r="DD3">
-        <v>122634.1400146484</v>
+        <v>67528.6875</v>
       </c>
       <c r="DE3">
-        <v>171157.9149169922</v>
+        <v>103794.09375</v>
       </c>
       <c r="DF3">
-        <v>74867.18896484375</v>
+        <v>49000.61728395062</v>
       </c>
       <c r="DG3">
-        <v>85627.9296875</v>
+        <v>61740.77777777777</v>
       </c>
       <c r="DH3">
-        <v>59965.24536132813</v>
+        <v>44100.55555555555</v>
       </c>
       <c r="DI3">
-        <v>105507.3120117188</v>
+        <v>77420.97530864197</v>
       </c>
       <c r="DJ3">
-        <v>128089.1275634766</v>
+        <v>124908.1646341463</v>
       </c>
       <c r="DK3">
-        <v>140858.2978515625</v>
+        <v>126033.4634146342</v>
       </c>
       <c r="DL3">
-        <v>122418.8438110352</v>
+        <v>115905.7743902439</v>
       </c>
       <c r="DM3">
-        <v>205949.7382202148</v>
+        <v>182298.4024390244</v>
       </c>
       <c r="DN3">
-        <v>69113.85424804688</v>
+        <v>61122.57851239669</v>
       </c>
       <c r="DO3">
-        <v>84399.74499511719</v>
+        <v>76114.90909090909</v>
       </c>
       <c r="DP3">
-        <v>50024.99523925781</v>
+        <v>47283.50413223141</v>
       </c>
       <c r="DQ3">
-        <v>70479.81567382813</v>
+        <v>86494.21487603306</v>
       </c>
       <c r="DR3">
-        <v>15172.44750976563</v>
+        <v>12476.0245398773</v>
       </c>
       <c r="DS3">
-        <v>26161.4680480957</v>
+        <v>23250.77300613497</v>
       </c>
       <c r="DT3">
-        <v>22659.67776489258</v>
+        <v>19281.12883435583</v>
       </c>
       <c r="DU3">
-        <v>27391.37377929688</v>
+        <v>22967.22699386503</v>
       </c>
       <c r="DV3">
-        <v>112284.6325683594</v>
+        <v>38316</v>
       </c>
       <c r="DW3">
-        <v>102428.840637207</v>
+        <v>45319.99999999999</v>
       </c>
       <c r="DX3">
-        <v>114339.9086303711</v>
+        <v>48615.99999999999</v>
       </c>
       <c r="DY3">
-        <v>114130.4612121582</v>
+        <v>52323.99999999999</v>
       </c>
       <c r="DZ3">
-        <v>59665.80322265625</v>
+        <v>31828.71812080537</v>
       </c>
       <c r="EA3">
-        <v>63303.37939453125</v>
+        <v>35605.0067114094</v>
       </c>
       <c r="EB3">
-        <v>48304.85083007813</v>
+        <v>25894.55033557047</v>
       </c>
       <c r="EC3">
-        <v>64070.95690917969</v>
+        <v>33986.59731543624</v>
       </c>
       <c r="ED3">
-        <v>31848.67886352539</v>
+        <v>16413.18238993711</v>
       </c>
       <c r="EE3">
-        <v>41336.69708251953</v>
+        <v>20003.56603773585</v>
       </c>
       <c r="EF3">
-        <v>19011.35064697266</v>
+        <v>8719.503144654089</v>
       </c>
       <c r="EG3">
-        <v>36801.04095458984</v>
+        <v>17951.91823899371</v>
       </c>
       <c r="EH3">
-        <v>39710.40502929688</v>
+        <v>15794.25641025641</v>
       </c>
       <c r="EI3">
-        <v>48839.03210449219</v>
+        <v>17074.87179487179</v>
       </c>
       <c r="EJ3">
-        <v>55850.03668212891</v>
+        <v>17928.61538461538</v>
       </c>
       <c r="EK3">
-        <v>54137.89709472656</v>
+        <v>20916.71794871795</v>
       </c>
       <c r="EL3">
-        <v>11874.712890625</v>
+        <v>9256.000000000002</v>
       </c>
       <c r="EM3">
-        <v>9566.355285644531</v>
+        <v>6942.000000000002</v>
       </c>
       <c r="EN3">
-        <v>11150.88557434082</v>
+        <v>8677.500000000002</v>
       </c>
       <c r="EO3">
-        <v>10953.34230041504</v>
+        <v>8214.700000000003</v>
       </c>
       <c r="EP3">
-        <v>10209.06927490234</v>
+        <v>10570.31055900621</v>
       </c>
       <c r="EQ3">
-        <v>21034.98809814453</v>
+        <v>17441.01242236025</v>
       </c>
       <c r="ER3">
-        <v>15005.63946533203</v>
+        <v>9513.27950310559</v>
       </c>
       <c r="ES3">
-        <v>17402.23815917969</v>
+        <v>13741.40372670808</v>
       </c>
       <c r="ET3">
-        <v>67938.18908691406</v>
+        <v>19865</v>
       </c>
       <c r="EU3">
-        <v>166360.8497314453</v>
+        <v>45210</v>
       </c>
       <c r="EV3">
-        <v>126478.8435058594</v>
+        <v>31510</v>
       </c>
       <c r="EW3">
-        <v>161114.9732666016</v>
+        <v>41100</v>
       </c>
       <c r="EX3">
-        <v>76777.06079101563</v>
+        <v>70243.71428571428</v>
       </c>
       <c r="EY3">
-        <v>84137.07385253906</v>
+        <v>81441.98757763975</v>
       </c>
       <c r="EZ3">
-        <v>76385.33642578125</v>
+        <v>74315.81366459627</v>
       </c>
       <c r="FA3">
-        <v>88435.31127929688</v>
+        <v>85514.08695652173</v>
       </c>
       <c r="FB3">
-        <v>129526.9857177734</v>
+        <v>23680.71951219512</v>
       </c>
       <c r="FC3">
-        <v>307868.1326904297</v>
+        <v>35162.28048780488</v>
       </c>
       <c r="FD3">
-        <v>129234.0931396484</v>
+        <v>25833.51219512195</v>
       </c>
       <c r="FE3">
-        <v>235046.227722168</v>
+        <v>38032.67073170732</v>
       </c>
       <c r="FF3">
-        <v>28867.12405395508</v>
+        <v>32630.73825503356</v>
       </c>
       <c r="FG3">
-        <v>47470.78814697266</v>
+        <v>48583.54362416107</v>
       </c>
       <c r="FH3">
-        <v>37565.29010009766</v>
+        <v>39156.88590604027</v>
       </c>
       <c r="FI3">
-        <v>32670.84112548828</v>
+        <v>34080.9932885906</v>
       </c>
       <c r="FJ3">
-        <v>55116.46856689453</v>
+        <v>18126.97435897436</v>
       </c>
       <c r="FK3">
-        <v>79533.64239501953</v>
+        <v>24805.33333333333</v>
       </c>
       <c r="FL3">
-        <v>54486.30261230469</v>
+        <v>14787.79487179487</v>
       </c>
       <c r="FM3">
-        <v>88772.45471191406</v>
+        <v>31006.66666666666</v>
       </c>
       <c r="FN3">
-        <v>96077.06103515625</v>
+        <v>58632.72727272727</v>
       </c>
       <c r="FO3">
-        <v>70196.1376953125</v>
+        <v>42508.72727272727</v>
       </c>
       <c r="FP3">
-        <v>79786.03881835938</v>
+        <v>48372</v>
       </c>
       <c r="FQ3">
-        <v>100456.6040039063</v>
+        <v>61564.36363636363</v>
       </c>
       <c r="FR3">
-        <v>114290.2341308594</v>
+        <v>46323.9477124183</v>
       </c>
       <c r="FS3">
-        <v>120538.8604125977</v>
+        <v>60397.04575163397</v>
       </c>
       <c r="FT3">
-        <v>118652.6946411133</v>
+        <v>49255.84313725489</v>
       </c>
       <c r="FU3">
-        <v>126705.0096435547</v>
+        <v>64501.69934640522</v>
       </c>
       <c r="FV3">
-        <v>43247.57052612305</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="FW3">
-        <v>32352.03155517578</v>
+        <v>22430.91603053435</v>
       </c>
       <c r="FX3">
-        <v>44302.95367431641</v>
+        <v>29028.24427480916</v>
       </c>
       <c r="FY3">
-        <v>58692.35870361328</v>
+        <v>42222.90076335878</v>
       </c>
       <c r="FZ3">
-        <v>82398.3046875</v>
+        <v>34075.56626506025</v>
       </c>
       <c r="GA3">
-        <v>54932.203125</v>
+        <v>22717.04417670683</v>
       </c>
       <c r="GB3">
-        <v>13733.05078125</v>
+        <v>5679.261044176707</v>
       </c>
       <c r="GC3">
-        <v>27466.1015625</v>
+        <v>11358.52208835341</v>
       </c>
       <c r="GD3">
-        <v>306739.9072265625</v>
+        <v>88898.64473684212</v>
       </c>
       <c r="GE3">
-        <v>402944.1727294922</v>
+        <v>105921.7894736842</v>
       </c>
       <c r="GF3">
-        <v>304736.5280761719</v>
+        <v>96464.48684210528</v>
       </c>
       <c r="GG3">
-        <v>379808.6964111328</v>
+        <v>105921.7894736842</v>
       </c>
       <c r="GH3">
-        <v>35117.3369140625</v>
+        <v>17794.86419753087</v>
       </c>
       <c r="GI3">
-        <v>143727.8048095703</v>
+        <v>33365.37037037037</v>
       </c>
       <c r="GJ3">
-        <v>108410.1628417969</v>
+        <v>20019.22222222223</v>
       </c>
       <c r="GK3">
-        <v>125149.7523193359</v>
+        <v>35589.72839506173</v>
       </c>
       <c r="GL3">
-        <v>128639.3366699219</v>
+        <v>60537.387283237</v>
       </c>
       <c r="GM3">
-        <v>98585.91430664063</v>
+        <v>45403.04046242775</v>
       </c>
       <c r="GN3">
-        <v>81184.62744140625</v>
+        <v>38523.79190751445</v>
       </c>
       <c r="GO3">
-        <v>108118.5883789063</v>
+        <v>52282.28901734105</v>
       </c>
       <c r="GP3">
-        <v>22042.56652832031</v>
+        <v>12256.9870967742</v>
       </c>
       <c r="GQ3">
-        <v>66600.01599121094</v>
+        <v>36770.96129032259</v>
       </c>
       <c r="GR3">
-        <v>36881.72241210938</v>
+        <v>20742.5935483871</v>
       </c>
       <c r="GS3">
-        <v>63256.28015136719</v>
+        <v>31113.89032258065</v>
       </c>
       <c r="GT3">
-        <v>211202.8186035156</v>
+        <v>86545.28859060403</v>
       </c>
       <c r="GU3">
-        <v>190427.6174316406</v>
+        <v>99166.47651006712</v>
       </c>
       <c r="GV3">
-        <v>184950.8747558594</v>
+        <v>82939.23489932886</v>
       </c>
       <c r="GW3">
-        <v>175986.5393066406</v>
+        <v>93757.39597315436</v>
       </c>
       <c r="GX3">
-        <v>22636.69287109375</v>
+        <v>11212.64516129032</v>
       </c>
       <c r="GY3">
-        <v>32009.94738769531</v>
+        <v>13882.32258064516</v>
       </c>
       <c r="GZ3">
-        <v>22369.70739746094</v>
+        <v>8542.967741935485</v>
       </c>
       <c r="HA3">
-        <v>38810.11340332031</v>
+        <v>16018.06451612903</v>
       </c>
       <c r="HB3">
-        <v>142708.1545410156</v>
+        <v>145211.5384615384</v>
       </c>
       <c r="HC3">
-        <v>132085.5460205078</v>
+        <v>135799.6794871795</v>
       </c>
       <c r="HD3">
-        <v>130675.7342529297</v>
+        <v>141177.8846153846</v>
       </c>
       <c r="HE3">
-        <v>156158.6331176758</v>
+        <v>165379.8076923077</v>
       </c>
       <c r="HF3">
-        <v>131981.6223144531</v>
+        <v>95796.14379084969</v>
       </c>
       <c r="HG3">
-        <v>166978.0813598633</v>
+        <v>133337.8758169935</v>
       </c>
       <c r="HH3">
-        <v>120750.7232055664</v>
+        <v>88028.88888888891</v>
       </c>
       <c r="HI3">
-        <v>117927.9946899414</v>
+        <v>95796.14379084969</v>
       </c>
       <c r="HJ3">
-        <v>22191.32257080078</v>
+        <v>24355.01234567901</v>
       </c>
       <c r="HK3">
-        <v>22578.0553894043</v>
+        <v>21978.91358024691</v>
       </c>
       <c r="HL3">
-        <v>15325.076171875</v>
+        <v>15147.62962962963</v>
       </c>
       <c r="HM3">
-        <v>19217.60214233398</v>
+        <v>20196.83950617284</v>
       </c>
       <c r="HN3">
-        <v>30671.77998352051</v>
+        <v>27914.35185185185</v>
       </c>
       <c r="HO3">
-        <v>23080.9861907959</v>
+        <v>22211.41975308642</v>
       </c>
       <c r="HP3">
-        <v>18304.55323791504</v>
+        <v>18309.41358024691</v>
       </c>
       <c r="HQ3">
-        <v>19995.4859161377</v>
+        <v>21310.95679012345</v>
       </c>
       <c r="HR3">
-        <v>168671.1983642578</v>
+        <v>69575.37974683543</v>
       </c>
       <c r="HS3">
-        <v>173840.2359924316</v>
+        <v>87530.31645569619</v>
       </c>
       <c r="HT3">
-        <v>86188.21475219727</v>
+        <v>58353.54430379746</v>
       </c>
       <c r="HU3">
-        <v>141424.3297119141</v>
+        <v>80797.2151898734</v>
       </c>
       <c r="HV3">
-        <v>63746.59545898438</v>
+        <v>44599.06586826347</v>
       </c>
       <c r="HW3">
-        <v>106694.7081298828</v>
+        <v>70776.77844311377</v>
       </c>
       <c r="HX3">
-        <v>76327.84631347656</v>
+        <v>55264.05988023952</v>
       </c>
       <c r="HY3">
-        <v>80466.30688476563</v>
+        <v>54294.51497005988</v>
       </c>
       <c r="HZ3">
-        <v>90447.21884155273</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="IA3">
-        <v>91060.13900756836</v>
+        <v>48571.98795180723</v>
       </c>
       <c r="IB3">
-        <v>89144.06875610352</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="IC3">
-        <v>84477.33901977539</v>
+        <v>53528.31325301205</v>
       </c>
       <c r="ID3">
-        <v>131404.5615234375</v>
+        <v>140059.5</v>
       </c>
       <c r="IE3">
-        <v>116878.9415283203</v>
+        <v>118800.46875</v>
       </c>
       <c r="IF3">
-        <v>131347.6142578125</v>
+        <v>127554.1875</v>
       </c>
       <c r="IG3">
-        <v>130958.4440917969</v>
+        <v>127554.1875</v>
       </c>
       <c r="IH3">
-        <v>119691.5768737793</v>
+        <v>79381</v>
       </c>
       <c r="II3">
-        <v>151295.2855529785</v>
+        <v>95061.1975308642</v>
       </c>
       <c r="IJ3">
-        <v>113468.7731018066</v>
+        <v>73500.92592592593</v>
       </c>
       <c r="IK3">
-        <v>139529.7712402344</v>
+        <v>93101.17283950617</v>
       </c>
       <c r="IL3">
-        <v>97653.71081542969</v>
+        <v>50638.44512195123</v>
       </c>
       <c r="IM3">
-        <v>123024.009765625</v>
+        <v>64142.03048780488</v>
       </c>
       <c r="IN3">
-        <v>122756.9658813477</v>
+        <v>51763.74390243903</v>
       </c>
       <c r="IO3">
-        <v>122748.6596069336</v>
+        <v>60766.13414634147</v>
       </c>
       <c r="IP3">
-        <v>300222.1003417969</v>
+        <v>53049.78512396694</v>
       </c>
       <c r="IQ3">
-        <v>299234.7979736328</v>
+        <v>61122.57851239669</v>
       </c>
       <c r="IR3">
-        <v>366688.8677978516</v>
+        <v>54203.04132231405</v>
       </c>
       <c r="IS3">
-        <v>326490.6356201172</v>
+        <v>62275.8347107438</v>
       </c>
       <c r="IT3">
-        <v>68064.72453308105</v>
+        <v>31190.06134969325</v>
       </c>
       <c r="IU3">
-        <v>70217.0173034668</v>
+        <v>30339.42331288343</v>
       </c>
       <c r="IV3">
-        <v>81474.15878295898</v>
+        <v>32607.79141104294</v>
       </c>
       <c r="IW3">
-        <v>71210.35330200195</v>
+        <v>31473.60736196319</v>
       </c>
       <c r="IX3">
-        <v>118636.4149169922</v>
+        <v>46555.99999999999</v>
       </c>
       <c r="IY3">
-        <v>122831.495300293</v>
+        <v>41199.99999999999</v>
       </c>
       <c r="IZ3">
-        <v>134877.5102539063</v>
+        <v>49027.99999999999</v>
       </c>
       <c r="JA3">
-        <v>145082.3936157227</v>
+        <v>53147.99999999999</v>
       </c>
       <c r="JB3">
-        <v>34437.85606384277</v>
+        <v>26973.48993288591</v>
       </c>
       <c r="JC3">
-        <v>50478.46473693848</v>
+        <v>39920.76510067114</v>
       </c>
       <c r="JD3">
-        <v>39596.41110229492</v>
+        <v>32907.6577181208</v>
       </c>
       <c r="JE3">
-        <v>46185.14227294922</v>
+        <v>44775.9932885906</v>
       </c>
       <c r="JF3">
-        <v>227215.1658325195</v>
+        <v>67191.46540880503</v>
       </c>
       <c r="JG3">
-        <v>190630.9176635742</v>
+        <v>56933.22641509434</v>
       </c>
       <c r="JH3">
-        <v>250002.6293334961</v>
+        <v>73346.40880503145</v>
       </c>
       <c r="JI3">
-        <v>238642.5345458984</v>
+        <v>63088.16981132075</v>
       </c>
       <c r="JJ3">
-        <v>128025.756149292</v>
+        <v>73848.82051282052</v>
       </c>
       <c r="JK3">
-        <v>95606.76109313965</v>
+        <v>50370.87179487179</v>
       </c>
       <c r="JL3">
-        <v>145834.3167419434</v>
+        <v>72141.33333333333</v>
       </c>
       <c r="JM3">
-        <v>130194.6992645264</v>
+        <v>62323.28205128205</v>
       </c>
       <c r="JN3">
-        <v>43695.21019744873</v>
+        <v>38643.8</v>
       </c>
       <c r="JO3">
-        <v>32904.56284713745</v>
+        <v>29156.4</v>
       </c>
       <c r="JP3">
-        <v>36876.07884216309</v>
+        <v>32280.3</v>
       </c>
       <c r="JQ3">
-        <v>40970.2685585022</v>
+        <v>36792.6</v>
       </c>
       <c r="JR3">
-        <v>54372.17523193359</v>
+        <v>46509.36645962734</v>
       </c>
       <c r="JS3">
-        <v>58429.41122436523</v>
+        <v>49680.4596273292</v>
       </c>
       <c r="JT3">
-        <v>56226.12835693359</v>
+        <v>49151.94409937889</v>
       </c>
       <c r="JU3">
-        <v>54984.77224731445</v>
+        <v>45452.33540372671</v>
       </c>
       <c r="JV3">
-        <v>91675.04922485352</v>
+        <v>28769.99999999999</v>
       </c>
       <c r="JW3">
-        <v>161171.2774963379</v>
+        <v>50004.99999999999</v>
       </c>
       <c r="JX3">
-        <v>80648.53570556641</v>
+        <v>29454.99999999999</v>
       </c>
       <c r="JY3">
-        <v>141800.4077148438</v>
+        <v>47949.99999999999</v>
       </c>
       <c r="JZ3">
-        <v>299525.4259643555</v>
+        <v>130307.1801242236</v>
       </c>
       <c r="KA3">
-        <v>326309.0322875977</v>
+        <v>133361.2546583851</v>
       </c>
       <c r="KB3">
-        <v>234392.6777954102</v>
+        <v>94676.3105590062</v>
       </c>
       <c r="KC3">
-        <v>280092.392578125</v>
+        <v>114018.7826086957</v>
       </c>
       <c r="KD3">
-        <v>80550.1708984375</v>
+        <v>60278.19512195121</v>
       </c>
       <c r="KE3">
-        <v>86267.35577392578</v>
+        <v>66018.97560975609</v>
       </c>
       <c r="KF3">
-        <v>67785.53344726563</v>
+        <v>48079.03658536585</v>
       </c>
       <c r="KG3">
-        <v>99899.70349121094</v>
+        <v>76782.93902439025</v>
       </c>
       <c r="KH3">
-        <v>114958.1827087402</v>
+        <v>47858.41610738255</v>
       </c>
       <c r="KI3">
-        <v>142540.8352203369</v>
+        <v>58010.20134228187</v>
       </c>
       <c r="KJ3">
-        <v>114118.469619751</v>
+        <v>57285.07382550335</v>
       </c>
       <c r="KK3">
-        <v>144125.0939025879</v>
+        <v>65261.47651006711</v>
       </c>
       <c r="KL3">
-        <v>53602.15167236328</v>
+        <v>22897.23076923077</v>
       </c>
       <c r="KM3">
-        <v>75849.84545898438</v>
+        <v>31483.6923076923</v>
       </c>
       <c r="KN3">
-        <v>41205.28686523438</v>
+        <v>19081.02564102564</v>
       </c>
       <c r="KO3">
-        <v>80506.30206298828</v>
+        <v>34345.84615384615</v>
       </c>
       <c r="KP3">
-        <v>202910.0549621582</v>
+        <v>206680.3636363636</v>
       </c>
       <c r="KQ3">
-        <v>191835.2662658691</v>
+        <v>237462.5454545454</v>
       </c>
       <c r="KR3">
-        <v>157838.8239440918</v>
+        <v>177364</v>
       </c>
       <c r="KS3">
-        <v>225569.4076538086</v>
+        <v>237462.5454545455</v>
       </c>
       <c r="KT3">
-        <v>179084.1236572266</v>
+        <v>45737.56862745097</v>
       </c>
       <c r="KU3">
-        <v>122191.4125366211</v>
+        <v>45737.56862745097</v>
       </c>
       <c r="KV3">
-        <v>149612.2430114746</v>
+        <v>50428.60130718954</v>
       </c>
       <c r="KW3">
-        <v>198989.490234375</v>
+        <v>51601.35947712418</v>
       </c>
       <c r="KX3">
-        <v>24502.69729614258</v>
+        <v>59375.95419847329</v>
       </c>
       <c r="KY3">
-        <v>28146.12422180176</v>
+        <v>59375.95419847329</v>
       </c>
       <c r="KZ3">
-        <v>23084.74444580078</v>
+        <v>48160.49618320611</v>
       </c>
       <c r="LA3">
-        <v>31926.95672607422</v>
+        <v>71910.87786259543</v>
       </c>
       <c r="LB3">
-        <v>37915284.14466095</v>
+        <v>20450740.2356909</v>
       </c>
     </row>
   </sheetData>
